--- a/ig/nr-update-location-identifier/ValueSet-fr-core-practitioner-qualification.xlsx
+++ b/ig/nr-update-location-identifier/ValueSet-fr-core-practitioner-qualification.xlsx
@@ -7,19 +7,19 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R48-DiplomeE" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R48-DiplomeE" r:id="rId4" sheetId="2"/>
     <sheet name="Include from TRE-R47-Commissi" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE-R49-DiplomeE" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE-R50-DESCGrou" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE-R51-DESCGrou" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE-R53-DiplomeP" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE-R54-DiplomeU" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE-R55-Certific" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE-R56-Attestat" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE-R52-Capacite" r:id="rId13" sheetId="11"/>
-    <sheet name="Include from TRE-R58-AutreTyp" r:id="rId14" sheetId="12"/>
-    <sheet name="Include from TRE-R36-AutreDip" r:id="rId15" sheetId="13"/>
-    <sheet name="Include from TRE-R226-Dip2iem" r:id="rId16" sheetId="14"/>
+    <sheet name="Include from TRE_R49-DiplomeE" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from TRE_R50-DESCGrou" r:id="rId7" sheetId="5"/>
+    <sheet name="Include from TRE_R51-DESCGrou" r:id="rId8" sheetId="6"/>
+    <sheet name="Include from TRE_R53-DiplomeP" r:id="rId9" sheetId="7"/>
+    <sheet name="Include from TRE_R54-DiplomeU" r:id="rId10" sheetId="8"/>
+    <sheet name="Include from TRE_R55-Certific" r:id="rId11" sheetId="9"/>
+    <sheet name="Include from TRE_R56-Attestat" r:id="rId12" sheetId="10"/>
+    <sheet name="Include from TRE_R52-Capacite" r:id="rId13" sheetId="11"/>
+    <sheet name="Include from TRE_R58-AutreTyp" r:id="rId14" sheetId="12"/>
+    <sheet name="Include from TRE_R36-AutreDip" r:id="rId15" sheetId="13"/>
+    <sheet name="Include from TRE_R226-Dip2iem" r:id="rId16" sheetId="14"/>
   </sheets>
 </workbook>
 </file>
@@ -72,7 +72,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:16:44+00:00</t>
+    <t>2023-12-20T16:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
